--- a/output/pdf_financials_xlsx/BDT.xlsx
+++ b/output/pdf_financials_xlsx/BDT.xlsx
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>174.854</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>199.441</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2372,22 +2372,22 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>164.033</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>208.158</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>246.519</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>246.519</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>157.151</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>180.244</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>190.191</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>174.854</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>199.441</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2482,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>164.033</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>208.158</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>246.519</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>246.519</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.705</v>
+        <v>158.856</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>180.244</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>190.191</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>222.822</v>
+        <v>47.968</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>229.375</v>
+        <v>29.934</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>215.613</v>
@@ -3142,22 +3142,22 @@
         <v>172.618</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>206.917</v>
+        <v>42.884</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>253.348</v>
+        <v>45.19</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>350.954</v>
+        <v>104.435</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>355.524</v>
+        <v>109.005</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>206.345</v>
+        <v>49.194</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>315.16</v>
+        <v>134.916</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>85.065</v>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -30922,7 +30922,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">

--- a/output/pdf_financials_xlsx/BDT.xlsx
+++ b/output/pdf_financials_xlsx/BDT.xlsx
@@ -6729,46 +6729,46 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>2.017</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>2.697</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.853</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>7.366</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>3.235</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.661</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>3.614</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>6.444</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>4.278</v>
       </c>
       <c r="P112" s="1" t="inlineStr">
         <is>
@@ -34640,7 +34640,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -36380,7 +36384,11 @@
           <t>Proceeds on sale of property and equipment 14</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37698,7 +37706,11 @@
           <t>Proceeds on sale of property and equipment 11</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -37792,7 +37804,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -40078,7 +40094,11 @@
           <t>Proceeds on sale of property and equipment 11</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -40172,7 +40192,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -42586,7 +42610,11 @@
           <t>Proceeds on sale of property and equipment 9</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -42680,7 +42708,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -45840,7 +45872,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -47258,7 +47294,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -48960,7 +49000,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -49054,7 +49098,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E438" s="5" t="n">
         <v>0.003</v>
       </c>
@@ -51146,7 +51194,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E460" s="5" t="n">
         <v>-0.612</v>
       </c>

--- a/output/pdf_financials_xlsx/BDT.xlsx
+++ b/output/pdf_financials_xlsx/BDT.xlsx
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-3.882</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -6906,25 +6906,25 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>3.903</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>7.157</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>15.861</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>1.469</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -43994,7 +43994,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -49290,7 +49294,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E440" s="5" t="n">
         <v>3.903</v>
       </c>
@@ -59018,7 +59026,11 @@
           <t>Net loss from discontinued operations (note 4)</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E545" s="5" t="n">
         <v>-3.882</v>
       </c>
